--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_h_6.xlsx
@@ -658,7 +658,7 @@
         <v>0.008432782635230575</v>
       </c>
       <c r="C2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>27527214</v>
+        <v>4244898</v>
       </c>
       <c r="L2" t="n">
-        <v>15683824</v>
+        <v>2186937</v>
       </c>
       <c r="M2" t="n">
-        <v>3820563</v>
+        <v>499052</v>
       </c>
       <c r="N2" t="n">
-        <v>120559</v>
+        <v>12799</v>
       </c>
       <c r="O2" t="n">
-        <v>2286434</v>
+        <v>313288</v>
       </c>
       <c r="P2" t="n">
-        <v>799383</v>
+        <v>113887</v>
       </c>
       <c r="Q2" t="n">
         <v>0.9999390244483948</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8920278549194336</v>
+        <v>0.8234401345252991</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7952367067337036</v>
+        <v>0.6671509742736816</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7393302321434021</v>
+        <v>0.578019917011261</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2698264420032501</v>
+        <v>0.1759022623300552</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7637345194816589</v>
+        <v>0.6293172836303711</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8804602026939392</v>
+        <v>0.7634763121604919</v>
       </c>
       <c r="X2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>28872412</v>
+        <v>4796855</v>
       </c>
       <c r="AG2" t="n">
-        <v>17836630</v>
+        <v>2983951</v>
       </c>
       <c r="AH2" t="n">
-        <v>4798928</v>
+        <v>801380</v>
       </c>
       <c r="AI2" t="n">
-        <v>353991</v>
+        <v>59049</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2755108</v>
+        <v>459641</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564692974090576</v>
+        <v>0.9560109972953796</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113166332244873</v>
+        <v>0.9115679264068604</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581637144088745</v>
+        <v>0.8585426211357117</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622001528739929</v>
+        <v>0.6615541577339172</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020119309425354</v>
+        <v>0.9020492434501648</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314349889755249</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002022202495942296</v>
       </c>
       <c r="C3" t="n">
-        <v>2172</v>
+        <v>362</v>
       </c>
       <c r="D3" t="n">
-        <v>27527214</v>
+        <v>4244898</v>
       </c>
       <c r="E3" t="n">
-        <v>2577279</v>
+        <v>743929</v>
       </c>
       <c r="F3" t="n">
-        <v>40073</v>
+        <v>17980</v>
       </c>
       <c r="G3" t="n">
-        <v>3189</v>
+        <v>1235</v>
       </c>
       <c r="H3" t="n">
-        <v>2195</v>
+        <v>1190</v>
       </c>
       <c r="I3" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>60097422</v>
+        <v>10016237</v>
       </c>
       <c r="K3" t="n">
-        <v>64493525</v>
+        <v>10409812</v>
       </c>
       <c r="L3" t="n">
-        <v>74338781</v>
+        <v>11959255</v>
       </c>
       <c r="M3" t="n">
-        <v>91034234</v>
+        <v>15030237</v>
       </c>
       <c r="N3" t="n">
-        <v>97116366</v>
+        <v>16180293</v>
       </c>
       <c r="O3" t="n">
-        <v>94214474</v>
+        <v>15635127</v>
       </c>
       <c r="P3" t="n">
-        <v>96709043</v>
+        <v>16100878</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9129437208175659</v>
+        <v>0.8473513126373291</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8001773953437805</v>
+        <v>0.6668999791145325</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6826909184455872</v>
+        <v>0.5337266325950623</v>
       </c>
       <c r="U3" t="n">
-        <v>0.225347712635994</v>
+        <v>0.143255278468132</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7482264041900635</v>
+        <v>0.6143636703491211</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6891084313392639</v>
+        <v>0.5887458920478821</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>28872412</v>
+        <v>4796855</v>
       </c>
       <c r="Z3" t="n">
-        <v>1187392</v>
+        <v>197460</v>
       </c>
       <c r="AA3" t="n">
-        <v>51135</v>
+        <v>8429</v>
       </c>
       <c r="AB3" t="n">
-        <v>40793</v>
+        <v>6823</v>
       </c>
       <c r="AC3" t="n">
-        <v>236</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>60099732</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>66511414</v>
+        <v>11099274</v>
       </c>
       <c r="AG3" t="n">
-        <v>76641422</v>
+        <v>12760866</v>
       </c>
       <c r="AH3" t="n">
-        <v>91588110</v>
+        <v>15262528</v>
       </c>
       <c r="AI3" t="n">
-        <v>97262032</v>
+        <v>16210047</v>
       </c>
       <c r="AJ3" t="n">
-        <v>94622500</v>
+        <v>15769750</v>
       </c>
       <c r="AK3" t="n">
-        <v>96738050</v>
+        <v>16122905</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575573801994324</v>
+        <v>0.9575310349464417</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100120067596436</v>
+        <v>0.9099469780921936</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575135469436646</v>
+        <v>0.8570606708526611</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6616765260696411</v>
+        <v>0.660917341709137</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015980958938599</v>
+        <v>0.9013646841049194</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312928318977356</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3126816</v>
+        <v>856943</v>
       </c>
       <c r="E4" t="n">
-        <v>15683824</v>
+        <v>2186937</v>
       </c>
       <c r="F4" t="n">
-        <v>713689</v>
+        <v>203150</v>
       </c>
       <c r="G4" t="n">
-        <v>21465</v>
+        <v>8061</v>
       </c>
       <c r="H4" t="n">
-        <v>51127</v>
+        <v>22404</v>
       </c>
       <c r="I4" t="n">
-        <v>3513</v>
+        <v>1763</v>
       </c>
       <c r="J4" t="n">
-        <v>2310</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>3331927</v>
+        <v>910180</v>
       </c>
       <c r="L4" t="n">
-        <v>4038385</v>
+        <v>1091087</v>
       </c>
       <c r="M4" t="n">
-        <v>1347037</v>
+        <v>364330</v>
       </c>
       <c r="N4" t="n">
-        <v>326243</v>
+        <v>59963</v>
       </c>
       <c r="O4" t="n">
-        <v>707321</v>
+        <v>184534</v>
       </c>
       <c r="P4" t="n">
-        <v>108532</v>
+        <v>35282</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9999695420265198</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9023646116256714</v>
+        <v>0.8352246284484863</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7976993322372437</v>
+        <v>0.6670255064964294</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7098826169967651</v>
+        <v>0.5549908876419067</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2455894351005554</v>
+        <v>0.157909020781517</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7559009194374084</v>
+        <v>0.6217505931854248</v>
       </c>
       <c r="W4" t="n">
-        <v>0.773120105266571</v>
+        <v>0.6648220419883728</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1226769</v>
+        <v>206052</v>
       </c>
       <c r="Z4" t="n">
-        <v>17836630</v>
+        <v>2983951</v>
       </c>
       <c r="AA4" t="n">
-        <v>496804</v>
+        <v>82537</v>
       </c>
       <c r="AB4" t="n">
-        <v>32965</v>
+        <v>5520</v>
       </c>
       <c r="AC4" t="n">
-        <v>6858</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1314038</v>
+        <v>220718</v>
       </c>
       <c r="AG4" t="n">
-        <v>1735744</v>
+        <v>289476</v>
       </c>
       <c r="AH4" t="n">
-        <v>793161</v>
+        <v>132039</v>
       </c>
       <c r="AI4" t="n">
-        <v>180577</v>
+        <v>30209</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299295</v>
+        <v>49911</v>
       </c>
       <c r="AK4" t="n">
-        <v>79525</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570130109786987</v>
+        <v>0.9567704200744629</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910663902759552</v>
+        <v>0.9107567667961121</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.85783851146698</v>
+        <v>0.8578009605407715</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619382500648499</v>
+        <v>0.6612355709075928</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018049240112305</v>
+        <v>0.9017068147659302</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313638806343079</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>132790</v>
+        <v>36508</v>
       </c>
       <c r="E5" t="n">
-        <v>1264559</v>
+        <v>290871</v>
       </c>
       <c r="F5" t="n">
-        <v>3820563</v>
+        <v>499052</v>
       </c>
       <c r="G5" t="n">
-        <v>92426</v>
+        <v>20147</v>
       </c>
       <c r="H5" t="n">
-        <v>267918</v>
+        <v>80934</v>
       </c>
       <c r="I5" t="n">
-        <v>18073</v>
+        <v>7521</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2624934</v>
+        <v>764710</v>
       </c>
       <c r="L5" t="n">
-        <v>3916610</v>
+        <v>1092321</v>
       </c>
       <c r="M5" t="n">
-        <v>1775766</v>
+        <v>435981</v>
       </c>
       <c r="N5" t="n">
-        <v>414432</v>
+        <v>76545</v>
       </c>
       <c r="O5" t="n">
-        <v>769371</v>
+        <v>196651</v>
       </c>
       <c r="P5" t="n">
-        <v>360642</v>
+        <v>79553</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9999763965606689</v>
       </c>
       <c r="R5" t="n">
-        <v>0.939201831817627</v>
+        <v>0.897432267665863</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9188080430030823</v>
+        <v>0.8662914037704468</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9681273698806763</v>
+        <v>0.9509901404380798</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9924403429031372</v>
+        <v>0.9916404485702515</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9849282503128052</v>
+        <v>0.9766567945480347</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9952114224433899</v>
+        <v>0.9929676651954651</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>48155</v>
+        <v>8093</v>
       </c>
       <c r="Z5" t="n">
-        <v>510890</v>
+        <v>85757</v>
       </c>
       <c r="AA5" t="n">
-        <v>4798928</v>
+        <v>801380</v>
       </c>
       <c r="AB5" t="n">
-        <v>59714</v>
+        <v>9985</v>
       </c>
       <c r="AC5" t="n">
-        <v>174844</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1279736</v>
+        <v>212753</v>
       </c>
       <c r="AG5" t="n">
-        <v>1763804</v>
+        <v>295307</v>
       </c>
       <c r="AH5" t="n">
-        <v>797401</v>
+        <v>133653</v>
       </c>
       <c r="AI5" t="n">
-        <v>181000</v>
+        <v>30295</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300697</v>
+        <v>50298</v>
       </c>
       <c r="AK5" t="n">
-        <v>79702</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735268950462341</v>
+        <v>0.9734548926353455</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642821550369263</v>
+        <v>0.9641887545585632</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837660789489746</v>
+        <v>0.9837294220924377</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963095784187317</v>
+        <v>0.9962948560714722</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938762187957764</v>
+        <v>0.9938633441925049</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998374879360199</v>
+        <v>0.9983736872673035</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>70219</v>
+        <v>15352</v>
       </c>
       <c r="E6" t="n">
-        <v>115968</v>
+        <v>20601</v>
       </c>
       <c r="F6" t="n">
-        <v>171934</v>
+        <v>28178</v>
       </c>
       <c r="G6" t="n">
-        <v>120559</v>
+        <v>12799</v>
       </c>
       <c r="H6" t="n">
-        <v>53483</v>
+        <v>11386</v>
       </c>
       <c r="I6" t="n">
-        <v>2704</v>
+        <v>1006</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>38779</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>32116</v>
+        <v>5368</v>
       </c>
       <c r="AA6" t="n">
-        <v>65335</v>
+        <v>10940</v>
       </c>
       <c r="AB6" t="n">
-        <v>353991</v>
+        <v>59049</v>
       </c>
       <c r="AC6" t="n">
-        <v>41884</v>
+        <v>6989</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1837</v>
+        <v>1313</v>
       </c>
       <c r="E7" t="n">
-        <v>76251</v>
+        <v>33462</v>
       </c>
       <c r="F7" t="n">
-        <v>405477</v>
+        <v>108498</v>
       </c>
       <c r="G7" t="n">
-        <v>201590</v>
+        <v>28400</v>
       </c>
       <c r="H7" t="n">
-        <v>2286434</v>
+        <v>313288</v>
       </c>
       <c r="I7" t="n">
-        <v>84216</v>
+        <v>24978</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4860</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>177905</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45512</v>
+        <v>7615</v>
       </c>
       <c r="AC7" t="n">
-        <v>2755108</v>
+        <v>459641</v>
       </c>
       <c r="AD7" t="n">
-        <v>72253</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>265</v>
+        <v>64</v>
       </c>
       <c r="E8" t="n">
-        <v>4328</v>
+        <v>2224</v>
       </c>
       <c r="F8" t="n">
-        <v>15864</v>
+        <v>6524</v>
       </c>
       <c r="G8" t="n">
-        <v>7573</v>
+        <v>2120</v>
       </c>
       <c r="H8" t="n">
-        <v>332598</v>
+        <v>68620</v>
       </c>
       <c r="I8" t="n">
-        <v>799383</v>
+        <v>113887</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1982</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1593</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75473</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
